--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646736</v>
+        <v>122646741</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>74762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549907</v>
+        <v>549935</v>
       </c>
       <c r="R2" t="n">
-        <v>7241957</v>
+        <v>7242044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646741</v>
+        <v>122646734</v>
       </c>
       <c r="B3" t="n">
-        <v>74762</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549935</v>
+        <v>549808</v>
       </c>
       <c r="R3" t="n">
-        <v>7242044</v>
+        <v>7241653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646825</v>
+        <v>122646826</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550018</v>
+        <v>550032</v>
       </c>
       <c r="R4" t="n">
-        <v>7242347</v>
+        <v>7242402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646740</v>
+        <v>122646733</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>91124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549939</v>
+        <v>549809</v>
       </c>
       <c r="R5" t="n">
-        <v>7242048</v>
+        <v>7241654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646733</v>
+        <v>122646825</v>
       </c>
       <c r="B6" t="n">
-        <v>91124</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549809</v>
+        <v>550018</v>
       </c>
       <c r="R6" t="n">
-        <v>7241654</v>
+        <v>7242347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646739</v>
+        <v>122646740</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549895</v>
+        <v>549939</v>
       </c>
       <c r="R7" t="n">
-        <v>7241985</v>
+        <v>7242048</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646826</v>
+        <v>122646736</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550032</v>
+        <v>549907</v>
       </c>
       <c r="R8" t="n">
-        <v>7242402</v>
+        <v>7241957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646734</v>
+        <v>122646747</v>
       </c>
       <c r="B9" t="n">
-        <v>90833</v>
+        <v>82443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549808</v>
+        <v>549986</v>
       </c>
       <c r="R9" t="n">
-        <v>7241653</v>
+        <v>7242297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646747</v>
+        <v>122646739</v>
       </c>
       <c r="B10" t="n">
-        <v>82443</v>
+        <v>90851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549986</v>
+        <v>549895</v>
       </c>
       <c r="R10" t="n">
-        <v>7242297</v>
+        <v>7241985</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646741</v>
+        <v>122646733</v>
       </c>
       <c r="B2" t="n">
-        <v>74762</v>
+        <v>91125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549935</v>
+        <v>549809</v>
       </c>
       <c r="R2" t="n">
-        <v>7242044</v>
+        <v>7241654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646734</v>
+        <v>122646826</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549808</v>
+        <v>550032</v>
       </c>
       <c r="R3" t="n">
-        <v>7241653</v>
+        <v>7242402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646826</v>
+        <v>122646739</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550032</v>
+        <v>549895</v>
       </c>
       <c r="R4" t="n">
-        <v>7242402</v>
+        <v>7241985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646733</v>
+        <v>122646747</v>
       </c>
       <c r="B5" t="n">
-        <v>91124</v>
+        <v>82444</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549809</v>
+        <v>549986</v>
       </c>
       <c r="R5" t="n">
-        <v>7241654</v>
+        <v>7242297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646825</v>
+        <v>122646734</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>90834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550018</v>
+        <v>549808</v>
       </c>
       <c r="R6" t="n">
-        <v>7242347</v>
+        <v>7241653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1208,7 @@
         <v>122646740</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646736</v>
+        <v>122646741</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>74763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549907</v>
+        <v>549935</v>
       </c>
       <c r="R8" t="n">
-        <v>7241957</v>
+        <v>7242044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646747</v>
+        <v>122646736</v>
       </c>
       <c r="B9" t="n">
-        <v>82443</v>
+        <v>90852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549986</v>
+        <v>549907</v>
       </c>
       <c r="R9" t="n">
-        <v>7242297</v>
+        <v>7241957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646739</v>
+        <v>122646825</v>
       </c>
       <c r="B10" t="n">
-        <v>90851</v>
+        <v>57537</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549895</v>
+        <v>550018</v>
       </c>
       <c r="R10" t="n">
-        <v>7241985</v>
+        <v>7242347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646733</v>
+        <v>122646736</v>
       </c>
       <c r="B2" t="n">
-        <v>91125</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549809</v>
+        <v>549907</v>
       </c>
       <c r="R2" t="n">
-        <v>7241654</v>
+        <v>7241957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122646826</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122646739</v>
       </c>
       <c r="B4" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122646747</v>
       </c>
       <c r="B5" t="n">
-        <v>82444</v>
+        <v>82447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646734</v>
+        <v>122646741</v>
       </c>
       <c r="B6" t="n">
-        <v>90834</v>
+        <v>74766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549808</v>
+        <v>549935</v>
       </c>
       <c r="R6" t="n">
-        <v>7241653</v>
+        <v>7242044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646740</v>
+        <v>122646733</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>91128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549939</v>
+        <v>549809</v>
       </c>
       <c r="R7" t="n">
-        <v>7242048</v>
+        <v>7241654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646741</v>
+        <v>122646825</v>
       </c>
       <c r="B8" t="n">
-        <v>74763</v>
+        <v>57537</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549935</v>
+        <v>550018</v>
       </c>
       <c r="R8" t="n">
-        <v>7242044</v>
+        <v>7242347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646736</v>
+        <v>122646740</v>
       </c>
       <c r="B9" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549907</v>
+        <v>549939</v>
       </c>
       <c r="R9" t="n">
-        <v>7241957</v>
+        <v>7242048</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646825</v>
+        <v>122646734</v>
       </c>
       <c r="B10" t="n">
-        <v>57537</v>
+        <v>90837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550018</v>
+        <v>549808</v>
       </c>
       <c r="R10" t="n">
-        <v>7242347</v>
+        <v>7241653</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646736</v>
+        <v>122646741</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>74766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549907</v>
+        <v>549935</v>
       </c>
       <c r="R2" t="n">
-        <v>7241957</v>
+        <v>7242044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646826</v>
+        <v>122646734</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550032</v>
+        <v>549808</v>
       </c>
       <c r="R3" t="n">
-        <v>7242402</v>
+        <v>7241653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646739</v>
+        <v>122646826</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549895</v>
+        <v>550032</v>
       </c>
       <c r="R4" t="n">
-        <v>7241985</v>
+        <v>7242402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646747</v>
+        <v>122646736</v>
       </c>
       <c r="B5" t="n">
-        <v>82447</v>
+        <v>90855</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549986</v>
+        <v>549907</v>
       </c>
       <c r="R5" t="n">
-        <v>7242297</v>
+        <v>7241957</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646741</v>
+        <v>122646733</v>
       </c>
       <c r="B6" t="n">
-        <v>74766</v>
+        <v>91128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549935</v>
+        <v>549809</v>
       </c>
       <c r="R6" t="n">
-        <v>7242044</v>
+        <v>7241654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646733</v>
+        <v>122646825</v>
       </c>
       <c r="B7" t="n">
-        <v>91128</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549809</v>
+        <v>550018</v>
       </c>
       <c r="R7" t="n">
-        <v>7241654</v>
+        <v>7242347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646825</v>
+        <v>122646739</v>
       </c>
       <c r="B8" t="n">
-        <v>57537</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550018</v>
+        <v>549895</v>
       </c>
       <c r="R8" t="n">
-        <v>7242347</v>
+        <v>7241985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646740</v>
+        <v>122646747</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>82447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549939</v>
+        <v>549986</v>
       </c>
       <c r="R9" t="n">
-        <v>7242048</v>
+        <v>7242297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646734</v>
+        <v>122646740</v>
       </c>
       <c r="B10" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549808</v>
+        <v>549939</v>
       </c>
       <c r="R10" t="n">
-        <v>7241653</v>
+        <v>7242048</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646825</v>
+        <v>122646733</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>91231</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550018</v>
+        <v>549809</v>
       </c>
       <c r="R4" t="n">
-        <v>7242347</v>
+        <v>7241654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646733</v>
+        <v>122646825</v>
       </c>
       <c r="B5" t="n">
-        <v>91231</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549809</v>
+        <v>550018</v>
       </c>
       <c r="R5" t="n">
-        <v>7241654</v>
+        <v>7242347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646747</v>
+        <v>122646826</v>
       </c>
       <c r="B2" t="n">
-        <v>82549</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549986</v>
+        <v>550032</v>
       </c>
       <c r="R2" t="n">
-        <v>7242297</v>
+        <v>7242402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646734</v>
+        <v>122646741</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>74868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549808</v>
+        <v>549935</v>
       </c>
       <c r="R3" t="n">
-        <v>7241653</v>
+        <v>7242044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646733</v>
+        <v>122646740</v>
       </c>
       <c r="B4" t="n">
-        <v>91231</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549809</v>
+        <v>549939</v>
       </c>
       <c r="R4" t="n">
-        <v>7241654</v>
+        <v>7242048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646825</v>
+        <v>122646733</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>91235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550018</v>
+        <v>549809</v>
       </c>
       <c r="R5" t="n">
-        <v>7242347</v>
+        <v>7241654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646736</v>
+        <v>122646739</v>
       </c>
       <c r="B6" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549907</v>
+        <v>549895</v>
       </c>
       <c r="R6" t="n">
-        <v>7241957</v>
+        <v>7241985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646741</v>
+        <v>122646747</v>
       </c>
       <c r="B7" t="n">
-        <v>74868</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549935</v>
+        <v>549986</v>
       </c>
       <c r="R7" t="n">
-        <v>7242044</v>
+        <v>7242297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646739</v>
+        <v>122646736</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549895</v>
+        <v>549907</v>
       </c>
       <c r="R8" t="n">
-        <v>7241985</v>
+        <v>7241957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646740</v>
+        <v>122646734</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549939</v>
+        <v>549808</v>
       </c>
       <c r="R9" t="n">
-        <v>7242048</v>
+        <v>7241653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646826</v>
+        <v>122646825</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550032</v>
+        <v>550018</v>
       </c>
       <c r="R10" t="n">
-        <v>7242402</v>
+        <v>7242347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646826</v>
+        <v>122646747</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550032</v>
+        <v>549986</v>
       </c>
       <c r="R2" t="n">
-        <v>7242402</v>
+        <v>7242297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646741</v>
+        <v>122646733</v>
       </c>
       <c r="B3" t="n">
-        <v>74868</v>
+        <v>91235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549935</v>
+        <v>549809</v>
       </c>
       <c r="R3" t="n">
-        <v>7242044</v>
+        <v>7241654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646733</v>
+        <v>122646825</v>
       </c>
       <c r="B5" t="n">
-        <v>91235</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549809</v>
+        <v>550018</v>
       </c>
       <c r="R5" t="n">
-        <v>7241654</v>
+        <v>7242347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646747</v>
+        <v>122646741</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>74868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549986</v>
+        <v>549935</v>
       </c>
       <c r="R7" t="n">
-        <v>7242297</v>
+        <v>7242044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646736</v>
+        <v>122646734</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549907</v>
+        <v>549808</v>
       </c>
       <c r="R8" t="n">
-        <v>7241957</v>
+        <v>7241653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646734</v>
+        <v>122646736</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549808</v>
+        <v>549907</v>
       </c>
       <c r="R9" t="n">
-        <v>7241653</v>
+        <v>7241957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646825</v>
+        <v>122646826</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550018</v>
+        <v>550032</v>
       </c>
       <c r="R10" t="n">
-        <v>7242347</v>
+        <v>7242402</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646747</v>
+        <v>122646741</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>74868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549986</v>
+        <v>549935</v>
       </c>
       <c r="R2" t="n">
-        <v>7242297</v>
+        <v>7242044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646733</v>
+        <v>122646739</v>
       </c>
       <c r="B3" t="n">
-        <v>91235</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549809</v>
+        <v>549895</v>
       </c>
       <c r="R3" t="n">
-        <v>7241654</v>
+        <v>7241985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646740</v>
+        <v>122646734</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549939</v>
+        <v>549808</v>
       </c>
       <c r="R4" t="n">
-        <v>7242048</v>
+        <v>7241653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646739</v>
+        <v>122646740</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549895</v>
+        <v>549939</v>
       </c>
       <c r="R6" t="n">
-        <v>7241985</v>
+        <v>7242048</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646741</v>
+        <v>122646826</v>
       </c>
       <c r="B7" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549935</v>
+        <v>550032</v>
       </c>
       <c r="R7" t="n">
-        <v>7242044</v>
+        <v>7242402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646734</v>
+        <v>122646736</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549808</v>
+        <v>549907</v>
       </c>
       <c r="R8" t="n">
-        <v>7241653</v>
+        <v>7241957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646736</v>
+        <v>122646733</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>91235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549907</v>
+        <v>549809</v>
       </c>
       <c r="R9" t="n">
-        <v>7241957</v>
+        <v>7241654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646826</v>
+        <v>122646747</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550032</v>
+        <v>549986</v>
       </c>
       <c r="R10" t="n">
-        <v>7242402</v>
+        <v>7242297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646741</v>
+        <v>122646740</v>
       </c>
       <c r="B2" t="n">
-        <v>74868</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549935</v>
+        <v>549939</v>
       </c>
       <c r="R2" t="n">
-        <v>7242044</v>
+        <v>7242048</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646739</v>
+        <v>122646826</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549895</v>
+        <v>550032</v>
       </c>
       <c r="R3" t="n">
-        <v>7241985</v>
+        <v>7242402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646734</v>
+        <v>122646733</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549808</v>
+        <v>549809</v>
       </c>
       <c r="R4" t="n">
-        <v>7241653</v>
+        <v>7241654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646825</v>
+        <v>122646734</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550018</v>
+        <v>549808</v>
       </c>
       <c r="R5" t="n">
-        <v>7242347</v>
+        <v>7241653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646740</v>
+        <v>122646736</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549939</v>
+        <v>549907</v>
       </c>
       <c r="R6" t="n">
-        <v>7242048</v>
+        <v>7241957</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646826</v>
+        <v>122646741</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550032</v>
+        <v>549935</v>
       </c>
       <c r="R7" t="n">
-        <v>7242402</v>
+        <v>7242044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646736</v>
+        <v>122646825</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549907</v>
+        <v>550018</v>
       </c>
       <c r="R8" t="n">
-        <v>7241957</v>
+        <v>7242347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646733</v>
+        <v>122646747</v>
       </c>
       <c r="B9" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549809</v>
+        <v>549986</v>
       </c>
       <c r="R9" t="n">
-        <v>7241654</v>
+        <v>7242297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646747</v>
+        <v>122646739</v>
       </c>
       <c r="B10" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549986</v>
+        <v>549895</v>
       </c>
       <c r="R10" t="n">
-        <v>7242297</v>
+        <v>7241985</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646740</v>
+        <v>122646734</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549939</v>
+        <v>549808</v>
       </c>
       <c r="R2" t="n">
-        <v>7242048</v>
+        <v>7241653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646826</v>
+        <v>122646733</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550032</v>
+        <v>549809</v>
       </c>
       <c r="R3" t="n">
-        <v>7242402</v>
+        <v>7241654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646733</v>
+        <v>122646826</v>
       </c>
       <c r="B4" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549809</v>
+        <v>550032</v>
       </c>
       <c r="R4" t="n">
-        <v>7241654</v>
+        <v>7242402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646734</v>
+        <v>122646825</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549808</v>
+        <v>550018</v>
       </c>
       <c r="R5" t="n">
-        <v>7241653</v>
+        <v>7242347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646736</v>
+        <v>122646747</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549907</v>
+        <v>549986</v>
       </c>
       <c r="R6" t="n">
-        <v>7241957</v>
+        <v>7242297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646741</v>
+        <v>122646739</v>
       </c>
       <c r="B7" t="n">
-        <v>74868</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549935</v>
+        <v>549895</v>
       </c>
       <c r="R7" t="n">
-        <v>7242044</v>
+        <v>7241985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646825</v>
+        <v>122646736</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550018</v>
+        <v>549907</v>
       </c>
       <c r="R8" t="n">
-        <v>7242347</v>
+        <v>7241957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646747</v>
+        <v>122646740</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549986</v>
+        <v>549939</v>
       </c>
       <c r="R9" t="n">
-        <v>7242297</v>
+        <v>7242048</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646739</v>
+        <v>122646741</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>74868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549895</v>
+        <v>549935</v>
       </c>
       <c r="R10" t="n">
-        <v>7241985</v>
+        <v>7242044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646734</v>
+        <v>122646733</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549808</v>
+        <v>549809</v>
       </c>
       <c r="R2" t="n">
-        <v>7241653</v>
+        <v>7241654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646733</v>
+        <v>122646734</v>
       </c>
       <c r="B3" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549809</v>
+        <v>549808</v>
       </c>
       <c r="R3" t="n">
-        <v>7241654</v>
+        <v>7241653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646826</v>
+        <v>122646740</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550032</v>
+        <v>549939</v>
       </c>
       <c r="R4" t="n">
-        <v>7242402</v>
+        <v>7242048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646747</v>
+        <v>122646826</v>
       </c>
       <c r="B6" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549986</v>
+        <v>550032</v>
       </c>
       <c r="R6" t="n">
-        <v>7242297</v>
+        <v>7242402</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646736</v>
+        <v>122646741</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>74868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549907</v>
+        <v>549935</v>
       </c>
       <c r="R8" t="n">
-        <v>7241957</v>
+        <v>7242044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646740</v>
+        <v>122646747</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549939</v>
+        <v>549986</v>
       </c>
       <c r="R9" t="n">
-        <v>7242048</v>
+        <v>7242297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646741</v>
+        <v>122646736</v>
       </c>
       <c r="B10" t="n">
-        <v>74868</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549935</v>
+        <v>549907</v>
       </c>
       <c r="R10" t="n">
-        <v>7242044</v>
+        <v>7241957</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646734</v>
+        <v>122646740</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549808</v>
+        <v>549939</v>
       </c>
       <c r="R3" t="n">
-        <v>7241653</v>
+        <v>7242048</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646740</v>
+        <v>122646825</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549939</v>
+        <v>550018</v>
       </c>
       <c r="R4" t="n">
-        <v>7242048</v>
+        <v>7242347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre hackmärken</t>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646825</v>
+        <v>122646734</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550018</v>
+        <v>549808</v>
       </c>
       <c r="R5" t="n">
-        <v>7242347</v>
+        <v>7241653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646740</v>
+        <v>122646734</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549939</v>
+        <v>549808</v>
       </c>
       <c r="R3" t="n">
-        <v>7242048</v>
+        <v>7241653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646825</v>
+        <v>122646740</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550018</v>
+        <v>549939</v>
       </c>
       <c r="R4" t="n">
-        <v>7242347</v>
+        <v>7242048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +967,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 ex lockande</t>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646734</v>
+        <v>122646825</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549808</v>
+        <v>550018</v>
       </c>
       <c r="R5" t="n">
-        <v>7241653</v>
+        <v>7242347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646733</v>
+        <v>122646736</v>
       </c>
       <c r="B2" t="n">
-        <v>91243</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549809</v>
+        <v>549907</v>
       </c>
       <c r="R2" t="n">
-        <v>7241654</v>
+        <v>7241957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646734</v>
+        <v>122646733</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549808</v>
+        <v>549809</v>
       </c>
       <c r="R3" t="n">
-        <v>7241653</v>
+        <v>7241654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646740</v>
+        <v>122646826</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549939</v>
+        <v>550032</v>
       </c>
       <c r="R4" t="n">
-        <v>7242048</v>
+        <v>7242402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646825</v>
+        <v>122646739</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550018</v>
+        <v>549895</v>
       </c>
       <c r="R5" t="n">
-        <v>7242347</v>
+        <v>7241985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646826</v>
+        <v>122646740</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550032</v>
+        <v>549939</v>
       </c>
       <c r="R6" t="n">
-        <v>7242402</v>
+        <v>7242048</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646739</v>
+        <v>122646825</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549895</v>
+        <v>550018</v>
       </c>
       <c r="R7" t="n">
-        <v>7241985</v>
+        <v>7242347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646747</v>
+        <v>122646734</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549986</v>
+        <v>549808</v>
       </c>
       <c r="R9" t="n">
-        <v>7242297</v>
+        <v>7241653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646736</v>
+        <v>122646747</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549907</v>
+        <v>549986</v>
       </c>
       <c r="R10" t="n">
-        <v>7241957</v>
+        <v>7242297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26191-2022 artfynd.xlsx
+++ b/artfynd/A 26191-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646736</v>
+        <v>122646733</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549907</v>
+        <v>549809</v>
       </c>
       <c r="R2" t="n">
-        <v>7241957</v>
+        <v>7241654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646733</v>
+        <v>122646734</v>
       </c>
       <c r="B3" t="n">
-        <v>91243</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549809</v>
+        <v>549808</v>
       </c>
       <c r="R3" t="n">
-        <v>7241654</v>
+        <v>7241653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646826</v>
+        <v>122646747</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550032</v>
+        <v>549986</v>
       </c>
       <c r="R4" t="n">
-        <v>7242402</v>
+        <v>7242297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646739</v>
+        <v>122646741</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549895</v>
+        <v>549935</v>
       </c>
       <c r="R5" t="n">
-        <v>7241985</v>
+        <v>7242044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646740</v>
+        <v>122646826</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549939</v>
+        <v>550032</v>
       </c>
       <c r="R6" t="n">
-        <v>7242048</v>
+        <v>7242402</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1150,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646825</v>
+        <v>122646740</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550018</v>
+        <v>549939</v>
       </c>
       <c r="R7" t="n">
-        <v>7242347</v>
+        <v>7242048</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 ex lockande</t>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646741</v>
+        <v>122646825</v>
       </c>
       <c r="B8" t="n">
-        <v>74868</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549935</v>
+        <v>550018</v>
       </c>
       <c r="R8" t="n">
-        <v>7242044</v>
+        <v>7242347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,6 +1359,11 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 ex lockande</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1420,218 +1385,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122646734</v>
-      </c>
-      <c r="B9" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>549808</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7241653</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>122646747</v>
-      </c>
-      <c r="B10" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>549986</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7242297</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>
